--- a/astro-site/public/dl/bar-checklist-templates/02-bar-station-checklists-cocktails-beer-wine.xlsx
+++ b/astro-site/public/dl/bar-checklist-templates/02-bar-station-checklists-cocktails-beer-wine.xlsx
@@ -1089,7 +1089,7 @@
       </c>
       <c r="B9" s="35" t="inlineStr">
         <is>
-          <t>Prep the day's infusions (if applicable: infused gin, spiced vodka)</t>
+          <t>Prep the day's infusions (if applicable: infused gin, spiced vodka) in labeled jars, never in a liquor bottle</t>
         </is>
       </c>
       <c r="C9" s="36" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="B11" s="35" t="inlineStr">
         <is>
-          <t>Keep the cocktail menu's allergens in writing and make sure the whole team knows where to find them: orgeat has ALMOND (tree nuts), sours EGG WHITE, flips MILK; sulfites in wine and vermouth are listed as a sensitivity (not one of the 9 major allergens; in the UK they are one of the 14)</t>
+          <t>Keep the cocktail menu's allergens in writing and make sure the whole team knows where to find them: orgeat has ALMOND (tree nuts), sours EGG WHITE, flips WHOLE EGG and often cream (MILK); sulfites in wine and vermouth are listed as a sensitivity (not one of the 9 major allergens; in the UK they are one of the 14)</t>
         </is>
       </c>
       <c r="C11" s="36" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B17" s="35" t="inlineStr">
         <is>
-          <t>Refill ice every hour (sooner at peak) ALWAYS with a scoop or tongs, never a glass: a broken glass means dumping the whole ice well. Ice is food: keep the scoop out of the ice or with the handle out</t>
+          <t>Refill ice every hour (sooner at peak) ALWAYS with a scoop or tongs, never a glass: a broken glass means dumping the whole ice well. Ice is food (FDA Food Code): keep the scoop out of the ice or with the handle out</t>
         </is>
       </c>
       <c r="C17" s="36" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="B7" s="35" t="inlineStr">
         <is>
-          <t>Flush the taps: pour off the first third until it runs clear</t>
+          <t>Flush the taps: pour off the first few ounces from each faucet until the beer runs clear and cold</t>
         </is>
       </c>
       <c r="C7" s="36" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Frequency</t>
+          <t>When</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="B6" s="35" t="inlineStr">
         <is>
-          <t>Check open wines by the glass (whites and roses in the cooler at 46–50 °F)</t>
+          <t>Check open wines by the glass (white and rosé wines in the cooler at 46–50 °F)</t>
         </is>
       </c>
       <c r="C6" s="36" t="inlineStr">
